--- a/public/post/drafts/season-prediction/ladies_model-exhaustive-tests-r2.xlsx
+++ b/public/post/drafts/season-prediction/ladies_model-exhaustive-tests-r2.xlsx
@@ -457,25 +457,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>0.657076490527484</v>
+        <v>0.655256956866819</v>
       </c>
       <c r="C3" t="n">
-        <v>0.681859247627968</v>
+        <v>0.686534960542947</v>
       </c>
       <c r="D3" t="n">
-        <v>0.329176268623909</v>
+        <v>0.325846099834329</v>
       </c>
       <c r="E3" t="n">
-        <v>0.388801717900085</v>
+        <v>0.390676853545011</v>
       </c>
       <c r="F3" t="n">
-        <v>0.75562324996716</v>
+        <v>0.768894233937521</v>
       </c>
       <c r="G3" t="n">
-        <v>0.745016537215409</v>
+        <v>0.749537870427246</v>
       </c>
       <c r="H3" t="n">
-        <v>0.592925585310336</v>
+        <v>0.596124495858979</v>
       </c>
     </row>
     <row r="4">
